--- a/Fahrzeug-Wiki/data/tn_batterycheck_bereinigt.xlsx
+++ b/Fahrzeug-Wiki/data/tn_batterycheck_bereinigt.xlsx
@@ -35875,7 +35875,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seat</t>
+          <t>Citroen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -35885,12 +35885,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Seat</t>
+          <t>Citroen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SEAT</t>
+          <t>Citroën</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -35914,7 +35914,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Skoda</t>
+          <t>Seat</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -35924,12 +35924,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Skoda</t>
+          <t>Seat</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Škoda</t>
+          <t>SEAT</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -35953,7 +35953,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mercedes</t>
+          <t>Skoda</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -35963,12 +35963,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mercedes</t>
+          <t>Skoda</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -35992,7 +35992,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Citroen</t>
+          <t>Mercedes</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -36002,12 +36002,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Citroen</t>
+          <t>Mercedes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Citroën</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -36101,7 +36101,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>geklärt: Werte korrekt (Software-Lock) – kann geschlossen werden</t>
+          <t>geklärt: Werte korrekt (Software-Lock) – geschlossen am 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -36123,7 +36123,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>korrigiert auf 48 / 45 kWh – kann geschlossen werden</t>
+          <t>korrigiert auf 48 / 45 kWh – geschlossen am 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -36167,7 +36167,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>korrigiert auf 95 / 86,5 kWh – kann geschlossen werden</t>
+          <t>korrigiert auf 95 / 86,5 kWh – geschlossen am 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -36189,7 +36189,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>geklärt: Zeile korrekt (156 PS, 11/2022–04/2025) – kann geschlossen werden</t>
+          <t>geklärt: Zeile korrekt (156 PS, 11/2022–04/2025) – geschlossen am 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -36233,7 +36233,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>korrigiert (Cooper E und SE netto) – kann geschlossen werden</t>
+          <t>korrigiert (Cooper E und SE netto) – geschlossen am 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -36255,7 +36255,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>korrigiert (xDrive40, xDrive50, M60) – kann geschlossen werden</t>
+          <t>korrigiert (xDrive40, xDrive50, M60) – geschlossen am 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -36343,7 +36343,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>geklärt: R75 nur mit Z.E. 40 (Zeile 317 entfernt), R90 Entry korrekt – kann geschlossen werden</t>
+          <t>geklärt: R75 nur mit Z.E. 40 (Zeile 317 entfernt), R90 Entry korrekt – geschlossen am 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -36387,7 +36387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>korrigiert – kann geschlossen werden</t>
+          <t>korrigiert – geschlossen am 2026-09-24</t>
         </is>
       </c>
     </row>
